--- a/assets-data.xlsx
+++ b/assets-data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="459">
   <si>
     <t>Asset Photo</t>
   </si>
@@ -35,6 +35,57 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Purchased from</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Serial No</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Assigned to</t>
+  </si>
+  <si>
+    <t>Date Created</t>
+  </si>
+  <si>
+    <t>Created by</t>
+  </si>
+  <si>
+    <t>Reservation</t>
+  </si>
+  <si>
+    <t>Leased to</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>Transact as a whole</t>
+  </si>
+  <si>
+    <t>Event Date</t>
+  </si>
+  <si>
+    <t>Event Due Date</t>
+  </si>
+  <si>
+    <t>Event Notes</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/83c1ca06-4d37-4c57-a0e2-16c88186c52b.jpg</t>
   </si>
   <si>
@@ -53,6 +104,27 @@
     <t>Available</t>
   </si>
   <si>
+    <t>Computer zone</t>
+  </si>
+  <si>
+    <t>650 va</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Bahria town tower</t>
+  </si>
+  <si>
+    <t>04/27/2026 07:21 PM</t>
+  </si>
+  <si>
+    <t>Dart IT</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/dac8a91c-f5f3-4a44-b6d2-75ae64abaa9d.jpg</t>
   </si>
   <si>
@@ -68,6 +140,15 @@
     <t>45,000.00</t>
   </si>
   <si>
+    <t>Arsalan naz plaza</t>
+  </si>
+  <si>
+    <t>MFP M277dw</t>
+  </si>
+  <si>
+    <t>04/22/2026 06:36 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/75e97905-673e-43c5-b74f-a7e49aa759bf.jpg</t>
   </si>
   <si>
@@ -83,6 +164,21 @@
     <t>170,000.00</t>
   </si>
   <si>
+    <t xml:space="preserve">Madina </t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Creatives</t>
+  </si>
+  <si>
+    <t>04/16/2026 08:55 PM</t>
+  </si>
+  <si>
+    <t>aizaz khan</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/f0dcd46e-e4d1-45cc-9b8e-85ff65079a0d.jpg</t>
   </si>
   <si>
@@ -101,6 +197,18 @@
     <t>Checked out</t>
   </si>
   <si>
+    <t>Abeer</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Zainab</t>
+  </si>
+  <si>
+    <t>04/13/2026 06:47 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/9f0bcacf-7ee4-42c4-b9e2-dab8f966ac20.jpg</t>
   </si>
   <si>
@@ -110,12 +218,18 @@
     <t>NEC 24inch</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>11,000.00</t>
   </si>
   <si>
+    <t>MA trader</t>
+  </si>
+  <si>
+    <t>Muhammad Kaleem</t>
+  </si>
+  <si>
+    <t>03/30/2026 11:24 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/cb9a3658-cd8f-4f74-9ca6-7b758f7751f0.jpg</t>
   </si>
   <si>
@@ -131,6 +245,15 @@
     <t>21,000.00</t>
   </si>
   <si>
+    <t>Ma Trader</t>
+  </si>
+  <si>
+    <t>Okasha</t>
+  </si>
+  <si>
+    <t>03/30/2026 11:21 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/64acfb6a-466a-4366-a434-049961c8ec3f.jpg</t>
   </si>
   <si>
@@ -146,6 +269,15 @@
     <t>223,200.00</t>
   </si>
   <si>
+    <t>Czone</t>
+  </si>
+  <si>
+    <t>925+</t>
+  </si>
+  <si>
+    <t>03/12/2026 11:16 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/627ae687-af6e-4d77-8d4b-464188635fc1.jpg</t>
   </si>
   <si>
@@ -161,6 +293,18 @@
     <t>28,000.00</t>
   </si>
   <si>
+    <t>Raheem laptop</t>
+  </si>
+  <si>
+    <t>Business Development</t>
+  </si>
+  <si>
+    <t>Aizaz</t>
+  </si>
+  <si>
+    <t>03/12/2026 10:17 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/cc4f9978-93a6-4ac6-8fab-38834fba9519.jpg</t>
   </si>
   <si>
@@ -173,6 +317,12 @@
     <t>100,000.00</t>
   </si>
   <si>
+    <t>Maheen Khan</t>
+  </si>
+  <si>
+    <t>03/12/2026 09:49 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/534ac174-82a6-479d-87d1-72bb3ed181f9.jpg</t>
   </si>
   <si>
@@ -185,6 +335,15 @@
     <t>70,000.00</t>
   </si>
   <si>
+    <t xml:space="preserve">Danish laptops </t>
+  </si>
+  <si>
+    <t>Muhammad Bilal Altaf</t>
+  </si>
+  <si>
+    <t>03/10/2026 09:29 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/8292d7e9-2854-48d1-a4dc-fedb893ec473.jpg</t>
   </si>
   <si>
@@ -197,6 +356,15 @@
     <t>Tplink</t>
   </si>
   <si>
+    <t>TL-WR844N</t>
+  </si>
+  <si>
+    <t>Lasma Tariq</t>
+  </si>
+  <si>
+    <t>02/25/2026 08:11 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/c36c8e04-af05-4f77-92ec-bf4eb3b79c16.jpg</t>
   </si>
   <si>
@@ -212,6 +380,15 @@
     <t>16,000.00</t>
   </si>
   <si>
+    <t>Nas plaza</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>02/16/2026 03:01 PM</t>
+  </si>
+  <si>
     <t>TAB001</t>
   </si>
   <si>
@@ -224,6 +401,15 @@
     <t>163,000.00</t>
   </si>
   <si>
+    <t>Serena - Mazhar</t>
+  </si>
+  <si>
+    <t>A2378</t>
+  </si>
+  <si>
+    <t>02/16/2026 02:44 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/1a464c19-919f-44b3-b59f-f0d517879545.jpg</t>
   </si>
   <si>
@@ -239,6 +425,9 @@
     <t>39,000.00</t>
   </si>
   <si>
+    <t>02/11/2026 12:38 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/21892571-e11e-4190-90fc-3e2bf05df265.jpg</t>
   </si>
   <si>
@@ -251,6 +440,9 @@
     <t>10,500.00</t>
   </si>
   <si>
+    <t>02/11/2026 12:34 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/b9929fae-bdb8-48bd-9ae6-e0081c5bae06.jpg</t>
   </si>
   <si>
@@ -266,6 +458,18 @@
     <t>55,000.00</t>
   </si>
   <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>I7, 16gb ram</t>
+  </si>
+  <si>
+    <t>Urooj Shahab</t>
+  </si>
+  <si>
+    <t>01/29/2026 01:35 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/9bde4981-1832-4324-a55c-d56f630b9ca0.jpg</t>
   </si>
   <si>
@@ -275,6 +479,9 @@
     <t>2,500.00</t>
   </si>
   <si>
+    <t>01/29/2026 01:32 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/b564761a-7886-4eac-9388-8c3a7f8b18d3.jpg</t>
   </si>
   <si>
@@ -287,6 +494,9 @@
     <t>50,000.00</t>
   </si>
   <si>
+    <t>01/20/2026 05:14 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/bb8f36da-b030-45a5-b08c-0141ff653156.jpg</t>
   </si>
   <si>
@@ -296,6 +506,12 @@
     <t>Dell inspiron</t>
   </si>
   <si>
+    <t>Wajiha Tahir</t>
+  </si>
+  <si>
+    <t>01/20/2026 05:12 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/82bdf3fe-5910-4372-a467-0d6924b3981e.jpg</t>
   </si>
   <si>
@@ -311,6 +527,15 @@
     <t>5,500.00</t>
   </si>
   <si>
+    <t>Z120</t>
+  </si>
+  <si>
+    <t>Computer equipment</t>
+  </si>
+  <si>
+    <t>01/14/2026 03:52 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/afc81cf0-fe6a-4b4f-a6dd-1881f297472c.jpg</t>
   </si>
   <si>
@@ -323,6 +548,9 @@
     <t>Steel seires</t>
   </si>
   <si>
+    <t>01/13/2026 09:13 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/db433f6f-94cd-401e-9c87-962e645810fe.jpg</t>
   </si>
   <si>
@@ -335,6 +563,9 @@
     <t>Alienware</t>
   </si>
   <si>
+    <t>01/13/2026 09:10 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/c4eb0ff6-3529-4714-8ad8-5e7095692d49.jpg</t>
   </si>
   <si>
@@ -347,6 +578,12 @@
     <t>2,800.00</t>
   </si>
   <si>
+    <t>SPK9617</t>
+  </si>
+  <si>
+    <t>01/13/2026 09:03 PM</t>
+  </si>
+  <si>
     <t>MAC02</t>
   </si>
   <si>
@@ -356,6 +593,15 @@
     <t>600,000.00</t>
   </si>
   <si>
+    <t>apple store USA</t>
+  </si>
+  <si>
+    <t>M3 PRO -512gb</t>
+  </si>
+  <si>
+    <t>01/06/2026 09:06 PM</t>
+  </si>
+  <si>
     <t>MAC01</t>
   </si>
   <si>
@@ -365,6 +611,18 @@
     <t>304,000.00</t>
   </si>
   <si>
+    <t>Raheem - Apple Shop</t>
+  </si>
+  <si>
+    <t>Macbook air - M4</t>
+  </si>
+  <si>
+    <t>Umair</t>
+  </si>
+  <si>
+    <t>01/06/2026 08:56 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/b3341083-8a8c-4509-a950-44045de25bf7.jpg</t>
   </si>
   <si>
@@ -377,6 +635,12 @@
     <t>1,000.00</t>
   </si>
   <si>
+    <t>Sameer Ahmed</t>
+  </si>
+  <si>
+    <t>01/06/2026 08:53 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/c048da2e-9c86-48e3-aedc-22a1fb9139dd.jpg</t>
   </si>
   <si>
@@ -386,6 +650,18 @@
     <t xml:space="preserve">Hp Laptop </t>
   </si>
   <si>
+    <t>Danish Laptop</t>
+  </si>
+  <si>
+    <t>15-da0xxx, i5 8gen, 8gb, 238gb ssd</t>
+  </si>
+  <si>
+    <t>S M Talha</t>
+  </si>
+  <si>
+    <t>01/06/2026 06:57 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/595bebdb-c9f7-41cd-9bf3-6beab2767f3c.jpg</t>
   </si>
   <si>
@@ -398,6 +674,12 @@
     <t>75,000.00</t>
   </si>
   <si>
+    <t>i5 10gen, 8gb, 256gb</t>
+  </si>
+  <si>
+    <t>01/06/2026 06:52 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/a44630f6-ec73-457e-a6eb-bcdef832dba5.jpg</t>
   </si>
   <si>
@@ -413,6 +695,15 @@
     <t>130,000.00</t>
   </si>
   <si>
+    <t>Danish laptop</t>
+  </si>
+  <si>
+    <t>M15, i7 10th gen, 16gb , 2x 256gb ssd, rx5500</t>
+  </si>
+  <si>
+    <t>01/06/2026 05:45 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/55deb0da-fa8b-4d5c-829d-53894e26fe13.jpg</t>
   </si>
   <si>
@@ -431,6 +722,12 @@
     <t>Disposed</t>
   </si>
   <si>
+    <t>01/06/2026 05:36 PM</t>
+  </si>
+  <si>
+    <t>adjusted 15000</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/3e5932c5-bffe-4368-985d-de5188f71b3f.jpg</t>
   </si>
   <si>
@@ -446,6 +743,18 @@
     <t>105,000.00</t>
   </si>
   <si>
+    <t>Danish laptops</t>
+  </si>
+  <si>
+    <t>I7 8th, 1060, 16gb, 500gbssd</t>
+  </si>
+  <si>
+    <t>Muhammad Zahid</t>
+  </si>
+  <si>
+    <t>01/06/2026 05:30 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/3c7fca8a-643f-405d-a94d-6511ab73ae57.jpg</t>
   </si>
   <si>
@@ -458,6 +767,12 @@
     <t>Lenovo</t>
   </si>
   <si>
+    <t>Raahim Ahmed Khan</t>
+  </si>
+  <si>
+    <t>01/06/2026 05:26 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/96dd83a4-2fa6-4607-9739-fc2e46f43a2e.jpg</t>
   </si>
   <si>
@@ -473,6 +788,12 @@
     <t>5,000.00</t>
   </si>
   <si>
+    <t xml:space="preserve">Naz plaza </t>
+  </si>
+  <si>
+    <t>01/06/2026 04:53 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/939abb3f-b1bf-4d25-827e-47975bf0d53b.jpg</t>
   </si>
   <si>
@@ -485,6 +806,13 @@
     <t>Naz plaza</t>
   </si>
   <si>
+    <t>01/06/2026 04:51 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">second monitor for gad pc_x000D_
+</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/984d1ae7-e5f3-41c6-96e4-ee2f1ff83a6d.jpg</t>
   </si>
   <si>
@@ -500,6 +828,15 @@
     <t>2,000.00</t>
   </si>
   <si>
+    <t>Osama pak gaming</t>
+  </si>
+  <si>
+    <t>Deathadder elite</t>
+  </si>
+  <si>
+    <t>01/06/2026 04:38 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/0d861d87-14e1-4c51-b70f-791c7eeb5968.jpg</t>
   </si>
   <si>
@@ -512,6 +849,12 @@
     <t>Steelseries</t>
   </si>
   <si>
+    <t>Osama- pak gaming</t>
+  </si>
+  <si>
+    <t>01/06/2026 04:37 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/cc45b2fd-7a5c-414f-8cc4-b78fc31e2ec3.jpg</t>
   </si>
   <si>
@@ -521,6 +864,9 @@
     <t>Reddragon mouse</t>
   </si>
   <si>
+    <t>01/06/2026 04:34 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/1359cdc2-4bec-4a93-991c-62e5200b5721.jpg</t>
   </si>
   <si>
@@ -533,6 +879,15 @@
     <t>Das</t>
   </si>
   <si>
+    <t>Osama - pak gaming</t>
+  </si>
+  <si>
+    <t>01/06/2026 04:32 PM</t>
+  </si>
+  <si>
+    <t>Subsolar PC</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/c8781687-4891-4831-a041-98e5129fc0c1.jpg</t>
   </si>
   <si>
@@ -548,6 +903,15 @@
     <t>3,000.00</t>
   </si>
   <si>
+    <t>Wired</t>
+  </si>
+  <si>
+    <t>Abdul Ahad</t>
+  </si>
+  <si>
+    <t>01/06/2026 04:31 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/6ec69303-0c19-4311-8a22-e563bddc04ca.jpg</t>
   </si>
   <si>
@@ -560,6 +924,9 @@
     <t>Steel series</t>
   </si>
   <si>
+    <t>01/06/2026 04:30 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/d94c8e3d-0187-483a-8fcf-46b335399c0e.jpg</t>
   </si>
   <si>
@@ -575,6 +942,15 @@
     <t>317,000.00</t>
   </si>
   <si>
+    <t>Xtreme Hardware</t>
+  </si>
+  <si>
+    <t>Ryzen 7 7700, msi 5060, 64gb, 2tb+ 512gb</t>
+  </si>
+  <si>
+    <t>01/05/2026 07:28 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/3fbfdcee-b994-4a74-95e1-7c1fc5cc9187.jpg</t>
   </si>
   <si>
@@ -587,6 +963,15 @@
     <t>185,000.00</t>
   </si>
   <si>
+    <t xml:space="preserve">Xtreme Hardware </t>
+  </si>
+  <si>
+    <t>Ryzen 7 5800x, 2060super, 32gb, 512gb</t>
+  </si>
+  <si>
+    <t>01/05/2026 07:25 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/09a1ffab-9a3c-44d4-9a77-057e60fc5f69.jpg</t>
   </si>
   <si>
@@ -599,6 +984,12 @@
     <t>270,000.00</t>
   </si>
   <si>
+    <t>Ryzen 7 3700x, Msi 3070ti, 32gb, 512gb +1tb ssd</t>
+  </si>
+  <si>
+    <t>01/05/2026 07:22 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/9c2f0fd2-c50f-427e-a321-0d7f5ff037ae.jpg</t>
   </si>
   <si>
@@ -614,6 +1005,12 @@
     <t>16,500.00</t>
   </si>
   <si>
+    <t>P24h2L</t>
+  </si>
+  <si>
+    <t>01/05/2026 07:19 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/c093c112-c925-4f65-a78b-2b32f1a2a27b.jpg</t>
   </si>
   <si>
@@ -626,6 +1023,15 @@
     <t xml:space="preserve">LG </t>
   </si>
   <si>
+    <t xml:space="preserve">Zah computer </t>
+  </si>
+  <si>
+    <t>4K HDR monitor</t>
+  </si>
+  <si>
+    <t>01/05/2026 07:17 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/bc713b86-131d-4911-9258-7b6038e521be.jpg</t>
   </si>
   <si>
@@ -635,6 +1041,18 @@
     <t>Thinkpad T480</t>
   </si>
   <si>
+    <t>Danish Laptops</t>
+  </si>
+  <si>
+    <t>T480, i7 8th, 256gb, 16gb</t>
+  </si>
+  <si>
+    <t>Syed Muhammad Hasan Jawaid</t>
+  </si>
+  <si>
+    <t>01/05/2026 04:13 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/94bbf106-1bd7-438b-be2e-28ff6cf8901d.jpg</t>
   </si>
   <si>
@@ -644,6 +1062,12 @@
     <t>Dell inspiron 5593</t>
   </si>
   <si>
+    <t>5593, i5 10th, 256gb, 8gb</t>
+  </si>
+  <si>
+    <t>01/05/2026 03:57 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/33ca8985-0122-4c7b-a2a6-5d37b085229d.jpg</t>
   </si>
   <si>
@@ -656,6 +1080,18 @@
     <t>36,000.00</t>
   </si>
   <si>
+    <t>Tech Traders</t>
+  </si>
+  <si>
+    <t>Rapture ac5300</t>
+  </si>
+  <si>
+    <t>01/05/2026 02:58 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Wifi </t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/82db318e-a143-4f75-97bb-eb221d0f8882.jpg</t>
   </si>
   <si>
@@ -671,6 +1107,15 @@
     <t>13,500.00</t>
   </si>
   <si>
+    <t>Tech traders</t>
+  </si>
+  <si>
+    <t>FG-30E</t>
+  </si>
+  <si>
+    <t>01/05/2026 02:36 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/7243c73b-7ee6-4149-bbdf-2db644223806.jpg</t>
   </si>
   <si>
@@ -683,6 +1128,18 @@
     <t>Lenvovo</t>
   </si>
   <si>
+    <t>T490</t>
+  </si>
+  <si>
+    <t>DL00687</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>01/05/2026 02:14 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/f3bd6ef4-6304-4471-9c6b-f9799765c694.jpg</t>
   </si>
   <si>
@@ -698,6 +1155,18 @@
     <t>32,000.00</t>
   </si>
   <si>
+    <t>Ali Fahim</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>1850402000931CA</t>
+  </si>
+  <si>
+    <t>01/05/2026 02:04 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/82edc529-1e18-4da8-8a32-3ac57eaefbc8.jpg</t>
   </si>
   <si>
@@ -710,6 +1179,18 @@
     <t>Under repair</t>
   </si>
   <si>
+    <t>Raheem -appleshop</t>
+  </si>
+  <si>
+    <t>Macbook air - intel i3</t>
+  </si>
+  <si>
+    <t>Model A2179</t>
+  </si>
+  <si>
+    <t>01/05/2026 01:49 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/02cc9b23-3a62-407d-a799-21aaa0494681.jpg</t>
   </si>
   <si>
@@ -722,6 +1203,12 @@
     <t>30,000.00</t>
   </si>
   <si>
+    <t>T470</t>
+  </si>
+  <si>
+    <t>01/05/2026 01:30 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/545c5c67-edc5-436d-9d43-42756efbe19a.jpg</t>
   </si>
   <si>
@@ -734,6 +1221,12 @@
     <t>Astro</t>
   </si>
   <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>01/05/2026 12:29 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/34597668-09a3-4471-8528-b671eff8991b.jpg</t>
   </si>
   <si>
@@ -743,6 +1236,9 @@
     <t>Headphones</t>
   </si>
   <si>
+    <t>01/05/2026 12:24 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/9ce54501-5aae-4f80-858e-54cd9eea8deb.jpg</t>
   </si>
   <si>
@@ -752,12 +1248,21 @@
     <t>Hyperx</t>
   </si>
   <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>01/05/2026 12:10 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/0b6b1119-3680-46f0-945a-426517a27de6.jpg</t>
   </si>
   <si>
     <t>HP005</t>
   </si>
   <si>
+    <t>01/05/2026 12:07 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/5ccfc908-7261-4c79-9e22-0549fa2fd2ec.jpg</t>
   </si>
   <si>
@@ -773,12 +1278,21 @@
     <t>4,000.00</t>
   </si>
   <si>
+    <t>SC 60 Usb ML</t>
+  </si>
+  <si>
+    <t>01/05/2026 11:59 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/e61da1c8-f19b-4510-89e2-324b43a8d817.jpg</t>
   </si>
   <si>
     <t>HP003</t>
   </si>
   <si>
+    <t>01/05/2026 11:12 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/ef163113-d914-486a-bdc4-7192b0e76612.jpg</t>
   </si>
   <si>
@@ -788,6 +1302,12 @@
     <t>HyperX</t>
   </si>
   <si>
+    <t xml:space="preserve">Abeer </t>
+  </si>
+  <si>
+    <t>01/05/2026 11:04 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/942e217a-dbc3-405c-9356-de0888425c0f.jpg</t>
   </si>
   <si>
@@ -797,6 +1317,12 @@
     <t>6,000.00</t>
   </si>
   <si>
+    <t>Blackshark v2</t>
+  </si>
+  <si>
+    <t>01/05/2026 11:01 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/135487cc-6e08-4647-a208-a3b228b2f969.jpg</t>
   </si>
   <si>
@@ -806,6 +1332,12 @@
     <t>Webcam</t>
   </si>
   <si>
+    <t>c925e</t>
+  </si>
+  <si>
+    <t>01/05/2026 10:56 AM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/03a8e04e-3dbb-4b1c-b476-d4fb19ad4881.jpg</t>
   </si>
   <si>
@@ -815,6 +1347,12 @@
     <t>Lenovo ThinkPad T50s</t>
   </si>
   <si>
+    <t>Umair Home</t>
+  </si>
+  <si>
+    <t>01/03/2026 05:01 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/db87795c-9692-4e29-b96b-1280dc3c0325.jpg</t>
   </si>
   <si>
@@ -827,6 +1365,9 @@
     <t>120,000.00</t>
   </si>
   <si>
+    <t>01/03/2026 04:35 PM</t>
+  </si>
+  <si>
     <t>https://www.assettiger.com/xp2/MAT/144560/Gallery/2db79aa7-291a-4ebe-9612-4e84f096854a.jpg</t>
   </si>
   <si>
@@ -837,6 +1378,18 @@
   </si>
   <si>
     <t>95,000.00</t>
+  </si>
+  <si>
+    <t>Blade stealth 13</t>
+  </si>
+  <si>
+    <t>CN0JJV9DCH20007N0BNCA01</t>
+  </si>
+  <si>
+    <t>Waniya Naushad</t>
+  </si>
+  <si>
+    <t>01/03/2026 04:32 PM</t>
   </si>
 </sst>
 </file>
@@ -894,7 +1447,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,108 +1472,342 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2">
         <v>46119</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2">
         <v>46133</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2">
         <v>46126</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2">
         <v>46108</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="2">
+        <v>46125</v>
+      </c>
+      <c r="X5" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>32</v>
@@ -1029,90 +1816,279 @@
         <v>46111</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="2">
+        <v>46113</v>
+      </c>
+      <c r="X6" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2">
         <v>46111</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q7" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" s="2">
+        <v>46113</v>
+      </c>
+      <c r="X7" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2">
         <v>46077</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2">
         <v>46093</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O9" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="P9" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q9" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X9" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>32</v>
@@ -1121,202 +2097,628 @@
         <v>46093</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="P10" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q10" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U10" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X10" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2">
         <v>46087</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="P11" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q11" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X11" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="E12" s="2">
         <v>46078</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="P12" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q12" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="2">
+        <v>46078</v>
+      </c>
+      <c r="X12" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="E13" s="2">
         <v>46008</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="P13" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q13" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V13" s="2">
+        <v>46069</v>
+      </c>
+      <c r="X13" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="E14" s="2">
         <v>46066</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="P14" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q14" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" s="2">
+        <v>46069</v>
+      </c>
+      <c r="X14" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2">
         <v>46064</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2">
         <v>46064</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q16" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="E17" s="2">
         <v>45856</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="P17" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q17" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U17" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V17" s="2">
+        <v>46037</v>
+      </c>
+      <c r="X17" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2">
         <v>46037</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="P18" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q18" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="2">
+        <v>46062</v>
+      </c>
+      <c r="X18" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>32</v>
@@ -1325,21 +2727,66 @@
         <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q19" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U19" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X19" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>32</v>
@@ -1348,153 +2795,489 @@
         <v>45719</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="P20" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q20" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="2">
+        <v>46048</v>
+      </c>
+      <c r="X20" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N21" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="P21" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q21" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U21" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V21" s="2">
+        <v>46036</v>
+      </c>
+      <c r="X21" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="E22" s="2">
         <v>46035</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P22" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q22" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" s="2">
+        <v>46125</v>
+      </c>
+      <c r="X22" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="E23" s="2">
         <v>46035</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O23" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q23" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="2">
+        <v>46035</v>
+      </c>
+      <c r="X23" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2">
         <v>46035</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O24" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="P24" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q24" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U24" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" s="2">
+        <v>46036</v>
+      </c>
+      <c r="X24" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2">
         <v>45397</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="P25" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q25" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V25" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X25" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2">
         <v>45937</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="P26" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q26" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X26" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>32</v>
@@ -1503,251 +3286,776 @@
         <v>45323</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O27" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="P27" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q27" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U27" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V27" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X27" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2">
         <v>45682</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O28" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="P28" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U28" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V28" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X28" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2">
         <v>45571</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="I29" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q29" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U29" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X29" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>128</v>
+        <v>222</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="E30" s="2">
         <v>46017</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>132</v>
+        <v>226</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O30" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q30" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U30" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V30" s="2">
+        <v>46029</v>
+      </c>
+      <c r="X30" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>135</v>
+        <v>232</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="E31" s="2">
         <v>45205</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>138</v>
+        <v>235</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q31" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U31" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V31" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X31" s="0" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>139</v>
+        <v>238</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>140</v>
+        <v>239</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>142</v>
+        <v>241</v>
       </c>
       <c r="E32" s="2">
         <v>45680</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O32" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="P32" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q32" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U32" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V32" s="2">
+        <v>46132</v>
+      </c>
+      <c r="X32" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>144</v>
+        <v>247</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>145</v>
+        <v>248</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E33" s="2">
         <v>45722</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="I33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O33" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="P33" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q33" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U33" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V33" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X33" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>148</v>
+        <v>253</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="E34" s="2">
         <v>45792</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H34" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="I34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q34" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U34" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X34" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>154</v>
+        <v>261</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="E35" s="2">
         <v>45728</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O35" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P35" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q35" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U35" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" s="2">
+        <v>46125</v>
+      </c>
+      <c r="W35" s="2">
+        <v>46125</v>
+      </c>
+      <c r="X35" s="0" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>159</v>
+        <v>268</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="E36" s="2">
         <v>45790</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>161</v>
+        <v>270</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M36" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O36" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="P36" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q36" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U36" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V36" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X36" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>162</v>
+        <v>274</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="E37" s="2">
         <v>45910</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="I37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O37" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="P37" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q37" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V37" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X37" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>166</v>
+        <v>280</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>168</v>
+        <v>282</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>32</v>
@@ -1756,654 +4064,2025 @@
         <v>45455</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>138</v>
+        <v>235</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="I38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M38" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q38" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U38" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V38" s="2">
+        <v>46035</v>
+      </c>
+      <c r="X38" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>170</v>
+        <v>285</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="E39" s="2">
         <v>45582</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="I39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M39" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O39" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q39" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U39" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V39" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X39" s="0" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>174</v>
+        <v>292</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="E40" s="2">
         <v>46002</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I40" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="J40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O40" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="P40" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q40" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U40" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" s="2">
+        <v>46035</v>
+      </c>
+      <c r="X40" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>178</v>
+        <v>299</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>180</v>
+        <v>301</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>181</v>
+        <v>302</v>
       </c>
       <c r="E41" s="2">
         <v>46028</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>161</v>
+        <v>270</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O41" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P41" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q41" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U41" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X41" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>184</v>
+        <v>306</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="E42" s="2">
         <v>45877</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="I42" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O42" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="P42" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q42" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U42" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V42" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X42" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>187</v>
+        <v>312</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>188</v>
+        <v>313</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>189</v>
+        <v>314</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="E43" s="2">
         <v>45798</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H43" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="I43" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O43" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="P43" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q43" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U43" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V43" s="2">
+        <v>46069</v>
+      </c>
+      <c r="X43" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>191</v>
+        <v>319</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>193</v>
+        <v>321</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="E44" s="2">
         <v>45514</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>194</v>
+        <v>322</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="I44" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O44" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P44" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q44" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U44" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V44" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X44" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>196</v>
+        <v>326</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>197</v>
+        <v>327</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>198</v>
+        <v>328</v>
       </c>
       <c r="E45" s="2">
         <v>46008</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>199</v>
+        <v>329</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H45" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="I45" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="J45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M45" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O45" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="P45" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q45" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U45" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V45" s="2">
+        <v>46113</v>
+      </c>
+      <c r="X45" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>202</v>
+        <v>334</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="E46" s="2">
         <v>45503</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H46" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="I46" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M46" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O46" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="P46" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q46" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U46" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V46" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X46" s="0" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>204</v>
+        <v>339</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>205</v>
+        <v>340</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E47" s="2">
         <v>45923</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="I47" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="J47" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O47" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="P47" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q47" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R47" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S47" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T47" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U47" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V47" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X47" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>207</v>
+        <v>346</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>208</v>
+        <v>347</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="E48" s="2">
         <v>45423</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="I48" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="J48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q48" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U48" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X48" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>210</v>
+        <v>351</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="E49" s="2">
         <v>45987</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>213</v>
+        <v>354</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H49" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="I49" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="J49" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L49" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O49" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="P49" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q49" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R49" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S49" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T49" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U49" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X49" s="0" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>214</v>
+        <v>359</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>215</v>
+        <v>360</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>216</v>
+        <v>361</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>217</v>
+        <v>362</v>
       </c>
       <c r="E50" s="2">
         <v>46006</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>218</v>
+        <v>363</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H50" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="I50" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="J50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K50" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M50" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O50" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="P50" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q50" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T50" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U50" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V50" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X50" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>219</v>
+        <v>367</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>221</v>
+        <v>369</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>222</v>
+        <v>370</v>
       </c>
       <c r="E51" s="2">
         <v>45953</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H51" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="I51" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="J51" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="K51" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N51" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="O51" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P51" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q51" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R51" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S51" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T51" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U51" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X51" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>224</v>
+        <v>376</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>225</v>
+        <v>377</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>226</v>
+        <v>378</v>
       </c>
       <c r="E52" s="2">
         <v>45777</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>227</v>
+        <v>379</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H52" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="I52" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="J52" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="K52" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L52" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M52" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N52" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="O52" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="P52" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q52" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R52" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S52" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T52" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U52" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V52" s="2">
+        <v>46028</v>
+      </c>
+      <c r="X52" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>228</v>
+        <v>384</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>229</v>
+        <v>385</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>230</v>
+        <v>386</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E53" s="2">
         <v>45931</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>231</v>
+        <v>387</v>
+      </c>
+      <c r="H53" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="I53" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="J53" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="K53" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L53" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M53" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N53" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O53" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P53" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q53" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R53" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S53" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T53" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U53" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V53" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X53" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>232</v>
+        <v>392</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>233</v>
+        <v>393</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>234</v>
+        <v>394</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E54" s="2">
         <v>45366</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>235</v>
+        <v>395</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="I54" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N54" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P54" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q54" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T54" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U54" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X54" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>237</v>
+        <v>399</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>238</v>
+        <v>400</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>239</v>
+        <v>401</v>
       </c>
       <c r="E55" s="2">
         <v>46008</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K55" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L55" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N55" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O55" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P55" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q55" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R55" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S55" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T55" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U55" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" s="2">
+        <v>46113</v>
+      </c>
+      <c r="X55" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>240</v>
+        <v>404</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>241</v>
+        <v>405</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E56" s="2">
         <v>45204</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K56" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M56" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P56" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q56" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T56" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U56" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X56" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>243</v>
+        <v>408</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>244</v>
+        <v>409</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>245</v>
+        <v>410</v>
       </c>
       <c r="E57" s="2">
         <v>45570</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I57" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K57" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L57" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N57" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O57" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="P57" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q57" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R57" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S57" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T57" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U57" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V57" s="2">
+        <v>46042</v>
+      </c>
+      <c r="X57" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>246</v>
+        <v>413</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>247</v>
+        <v>414</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>239</v>
+        <v>401</v>
       </c>
       <c r="E58" s="2">
         <v>46008</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I58" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K58" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L58" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N58" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O58" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="P58" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q58" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R58" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S58" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T58" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U58" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V58" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X58" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>248</v>
+        <v>416</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>249</v>
+        <v>417</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>251</v>
+        <v>419</v>
       </c>
       <c r="E59" s="2">
         <v>46027</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>252</v>
+        <v>420</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H59" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I59" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K59" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N59" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O59" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="P59" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q59" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U59" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V59" s="2">
+        <v>46093</v>
+      </c>
+      <c r="X59" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>253</v>
+        <v>423</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>254</v>
+        <v>424</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>238</v>
+        <v>400</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>245</v>
+        <v>410</v>
       </c>
       <c r="E60" s="2">
         <v>45918</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H60" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I60" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K60" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L60" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N60" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O60" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="P60" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q60" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R60" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S60" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T60" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U60" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V60" s="2">
+        <v>46042</v>
+      </c>
+      <c r="X60" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>255</v>
+        <v>426</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>256</v>
+        <v>427</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>257</v>
+        <v>428</v>
       </c>
       <c r="E61" s="2">
         <v>45931</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H61" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="I61" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="J61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K61" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M61" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N61" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="O61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P61" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q61" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T61" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U61" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X61" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>258</v>
+        <v>431</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>259</v>
+        <v>432</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="E62" s="2">
         <v>45174</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H62" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="I62" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K62" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L62" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M62" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N62" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O62" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P62" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q62" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R62" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S62" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T62" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U62" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X62" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>261</v>
+        <v>436</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>262</v>
+        <v>437</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>263</v>
+        <v>438</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="E63" s="2">
         <v>45985</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="H63" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="I63" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="J63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K63" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M63" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P63" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q63" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T63" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U63" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="X63" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>264</v>
+        <v>441</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>265</v>
+        <v>442</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>266</v>
+        <v>443</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E64" s="2">
         <v>44564</v>
       </c>
       <c r="F64" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="G64" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="G64" s="0" t="s">
-        <v>138</v>
+      <c r="H64" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="I64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K64" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M64" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P64" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q64" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U64" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V64" s="2">
+        <v>46025</v>
+      </c>
+      <c r="X64" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>267</v>
+        <v>446</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>268</v>
+        <v>447</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>269</v>
+        <v>448</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E65" s="2">
         <v>46011</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>270</v>
+        <v>449</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H65" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="I65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="J65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K65" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M65" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N65" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="O65" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="P65" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q65" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U65" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V65" s="2">
+        <v>46132</v>
+      </c>
+      <c r="X65" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>271</v>
+        <v>451</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>272</v>
+        <v>452</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>273</v>
+        <v>453</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="E66" s="2">
         <v>45386</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>274</v>
+        <v>454</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="H66" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="I66" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="J66" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="K66" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L66" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="N66" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="O66" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="P66" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q66" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="R66" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S66" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T66" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="U66" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="V66" s="2">
+        <v>46029</v>
+      </c>
+      <c r="X66" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
